--- a/results/autoarc_workbook_with_details.xlsx
+++ b/results/autoarc_workbook_with_details.xlsx
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ladder:ai:100</t>
+          <t>ladder:ai:100:deaths; ladder:ai:100:damages</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1110,7 +1110,11 @@
   * Exclude purely notional losses such as declines in market capitalization or share price that do not correspond to real resource costs. Give all estimates in 2026 USD.  
 * Resolution sources: Assume access to authoritative assessments, which may include estimates from the WHO, World Bank, IMF, national cybersecurity agencies (e.g., CISA, ENISA), major insurers and reinsurers, incident-response and threat-intelligence firms, and academic epidemiological and economic-modeling groups. Where multiple analyses exist, we will use the consensus or median; absent that, we will defer to the majority opinion of a panel of at least five experts.
 [DATES]
-* The incident must have an onset before the end of the defined year.</t>
+* Count only incidents whose onset falls within the specified counting interval, beginning on the elicitation date. All dates refer to UTC calendar dates, inclusive of the stated start and end dates.
+* For six- and twelve-month horizons, the interval ends that many calendar months after the elicitation date. For a fixed-year horizon, it ends on December 31 of the named year. The exact start and end dates are supplied with this forecast. Every later elicitation starts a new counting interval; there is no permanent project-start or calendar-year baseline.
+* Exclude incidents that began before the interval, including their later harms. New reporting, additional losses or later AI involvement does not by itself establish a new incident onset.
+* For each eligible incident, count attributable mortality, equivalent morbidity and economic damages within its first three years after onset, under the severity definitions above. Harm after the interval's end date can count if it falls within that incident's three-year harm window. The horizon is an onset deadline, not a deadline for all harm to occur.
+* These date rules apply to all four incident categories only; the separate large-scale-catastrophe and human-disempowerment questions retain their own date criteria.</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1149,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ladder:ai:1k</t>
+          <t>ladder:ai:1k:deaths; ladder:ai:1k:damages</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1179,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ladder:ai:10k</t>
+          <t>ladder:ai:10k:deaths; ladder:ai:10k:damages</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1210,7 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ladder:ai:100k</t>
+          <t>ladder:ai:100k:deaths; ladder:ai:100k:damages</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1245,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ladder:ai:1M</t>
+          <t>ladder:ai:1M:deaths; ladder:ai:1M:damages</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1275,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ladder:ai:10M</t>
+          <t>ladder:ai:10M:deaths; ladder:ai:10M:damages</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1305,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ladder:ai:100M</t>
+          <t>ladder:ai:100M:deaths; ladder:ai:100M:damages</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1335,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ladder:ai:1B</t>
+          <t>ladder:ai:1B:deaths; ladder:ai:1B:damages</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1365,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ladder:ai:100</t>
+          <t>ladder:ai:100:deaths; ladder:ai:100:damages</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1395,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ladder:ai:1k</t>
+          <t>ladder:ai:1k:deaths; ladder:ai:1k:damages</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1425,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ladder:ai:10k</t>
+          <t>ladder:ai:10k:deaths; ladder:ai:10k:damages</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1455,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ladder:ai:100k</t>
+          <t>ladder:ai:100k:deaths; ladder:ai:100k:damages</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ladder:ai:1M</t>
+          <t>ladder:ai:1M:deaths; ladder:ai:1M:damages</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1520,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ladder:ai:10M</t>
+          <t>ladder:ai:10M:deaths; ladder:ai:10M:damages</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1550,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ladder:ai:100M</t>
+          <t>ladder:ai:100M:deaths; ladder:ai:100M:damages</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1580,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ladder:ai:1B</t>
+          <t>ladder:ai:1B:deaths; ladder:ai:1B:damages</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1610,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ladder:ai:100</t>
+          <t>ladder:ai:100:deaths; ladder:ai:100:damages</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1640,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ladder:ai:1k</t>
+          <t>ladder:ai:1k:deaths; ladder:ai:1k:damages</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1670,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ladder:ai:10k</t>
+          <t>ladder:ai:10k:deaths; ladder:ai:10k:damages</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1701,7 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ladder:ai:100k</t>
+          <t>ladder:ai:100k:deaths; ladder:ai:100k:damages</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ladder:ai:1M</t>
+          <t>ladder:ai:1M:deaths; ladder:ai:1M:damages</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1766,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ladder:ai:10M</t>
+          <t>ladder:ai:10M:deaths; ladder:ai:10M:damages</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1796,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ladder:ai:100M</t>
+          <t>ladder:ai:100M:deaths; ladder:ai:100M:damages</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1826,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ladder:ai:1B</t>
+          <t>ladder:ai:1B:deaths; ladder:ai:1B:damages</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1856,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ladder:ai:100</t>
+          <t>ladder:ai:100:deaths; ladder:ai:100:damages</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1886,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ladder:ai:1k</t>
+          <t>ladder:ai:1k:deaths; ladder:ai:1k:damages</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1916,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ladder:ai:10k</t>
+          <t>ladder:ai:10k:deaths; ladder:ai:10k:damages</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1947,7 @@
       <c r="F38" s="14" t="n"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ladder:ai:100k</t>
+          <t>ladder:ai:100k:deaths; ladder:ai:100k:damages</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1982,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ladder:ai:1M</t>
+          <t>ladder:ai:1M:deaths; ladder:ai:1M:damages</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2012,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ladder:ai:10M</t>
+          <t>ladder:ai:10M:deaths; ladder:ai:10M:damages</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2042,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ladder:ai:100M</t>
+          <t>ladder:ai:100M:deaths; ladder:ai:100M:damages</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ladder:ai:1B</t>
+          <t>ladder:ai:1B:deaths; ladder:ai:1B:damages</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ladder:bio:100</t>
+          <t>ladder:bio:100:deaths; ladder:bio:100:damages</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2127,7 +2131,11 @@
   * Exclude purely notional losses such as declines in market capitalization or share price that do not correspond to real resource costs. Give all estimates in 2026 USD.  
 * Resolution sources: Assume access to authoritative assessments, which may include estimates from the WHO, World Bank, IMF, national cybersecurity agencies (e.g., CISA, ENISA), major insurers and reinsurers, incident-response and threat-intelligence firms, and academic epidemiological and economic-modeling groups. Where multiple analyses exist, we will use the consensus or median; absent that, we will defer to the majority opinion of a panel of at least five experts.
 [DATES]
-* The incident must have an onset before the end of the defined year.</t>
+* Count only incidents whose onset falls within the specified counting interval, beginning on the elicitation date. All dates refer to UTC calendar dates, inclusive of the stated start and end dates.
+* For six- and twelve-month horizons, the interval ends that many calendar months after the elicitation date. For a fixed-year horizon, it ends on December 31 of the named year. The exact start and end dates are supplied with this forecast. Every later elicitation starts a new counting interval; there is no permanent project-start or calendar-year baseline.
+* Exclude incidents that began before the interval, including their later harms. New reporting, additional losses or later AI involvement does not by itself establish a new incident onset.
+* For each eligible incident, count attributable mortality, equivalent morbidity and economic damages within its first three years after onset, under the severity definitions above. Harm after the interval's end date can count if it falls within that incident's three-year harm window. The horizon is an onset deadline, not a deadline for all harm to occur.
+* These date rules apply to all four incident categories only; the separate large-scale-catastrophe and human-disempowerment questions retain their own date criteria.</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2170,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ladder:bio:1k</t>
+          <t>ladder:bio:1k:deaths; ladder:bio:1k:damages</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ladder:bio:10k</t>
+          <t>ladder:bio:10k:deaths; ladder:bio:10k:damages</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2231,7 @@
       <c r="F46" s="14" t="n"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ladder:bio:100k</t>
+          <t>ladder:bio:100k:deaths; ladder:bio:100k:damages</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2266,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ladder:bio:1M</t>
+          <t>ladder:bio:1M:deaths; ladder:bio:1M:damages</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2296,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ladder:bio:10M</t>
+          <t>ladder:bio:10M:deaths; ladder:bio:10M:damages</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2326,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ladder:bio:100M</t>
+          <t>ladder:bio:100M:deaths; ladder:bio:100M:damages</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2356,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ladder:bio:1B</t>
+          <t>ladder:bio:1B:deaths; ladder:bio:1B:damages</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2386,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ladder:bio:100</t>
+          <t>ladder:bio:100:deaths; ladder:bio:100:damages</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2416,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ladder:bio:1k</t>
+          <t>ladder:bio:1k:deaths; ladder:bio:1k:damages</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2446,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ladder:bio:10k</t>
+          <t>ladder:bio:10k:deaths; ladder:bio:10k:damages</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2477,7 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ladder:bio:100k</t>
+          <t>ladder:bio:100k:deaths; ladder:bio:100k:damages</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2512,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ladder:bio:1M</t>
+          <t>ladder:bio:1M:deaths; ladder:bio:1M:damages</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2542,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ladder:bio:10M</t>
+          <t>ladder:bio:10M:deaths; ladder:bio:10M:damages</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2572,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ladder:bio:100M</t>
+          <t>ladder:bio:100M:deaths; ladder:bio:100M:damages</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2602,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ladder:bio:1B</t>
+          <t>ladder:bio:1B:deaths; ladder:bio:1B:damages</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2632,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ladder:bio:100</t>
+          <t>ladder:bio:100:deaths; ladder:bio:100:damages</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2662,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ladder:bio:1k</t>
+          <t>ladder:bio:1k:deaths; ladder:bio:1k:damages</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ladder:bio:10k</t>
+          <t>ladder:bio:10k:deaths; ladder:bio:10k:damages</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2723,7 @@
       <c r="F62" s="14" t="n"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ladder:bio:100k</t>
+          <t>ladder:bio:100k:deaths; ladder:bio:100k:damages</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2758,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ladder:bio:1M</t>
+          <t>ladder:bio:1M:deaths; ladder:bio:1M:damages</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2788,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ladder:bio:10M</t>
+          <t>ladder:bio:10M:deaths; ladder:bio:10M:damages</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2818,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ladder:bio:100M</t>
+          <t>ladder:bio:100M:deaths; ladder:bio:100M:damages</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2848,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ladder:bio:1B</t>
+          <t>ladder:bio:1B:deaths; ladder:bio:1B:damages</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2878,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ladder:bio:100</t>
+          <t>ladder:bio:100:deaths; ladder:bio:100:damages</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2908,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ladder:bio:1k</t>
+          <t>ladder:bio:1k:deaths; ladder:bio:1k:damages</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2938,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ladder:bio:10k</t>
+          <t>ladder:bio:10k:deaths; ladder:bio:10k:damages</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2969,7 @@
       <c r="F70" s="14" t="n"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ladder:bio:100k</t>
+          <t>ladder:bio:100k:deaths; ladder:bio:100k:damages</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3004,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ladder:bio:1M</t>
+          <t>ladder:bio:1M:deaths; ladder:bio:1M:damages</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3034,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ladder:bio:10M</t>
+          <t>ladder:bio:10M:deaths; ladder:bio:10M:damages</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3064,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ladder:bio:100M</t>
+          <t>ladder:bio:100M:deaths; ladder:bio:100M:damages</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3099,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ladder:bio:1B</t>
+          <t>ladder:bio:1B:deaths; ladder:bio:1B:damages</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3129,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ladder:cyber:100</t>
+          <t>ladder:cyber:100:deaths; ladder:cyber:100:damages</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>* A set of malicious cyber operations sharing a common perpetrator (an individual, group, or coordinated set of actors) and a common campaign or method, directed at a target or set of related targets within a bounded, contiguous period.   
+  * Treat a campaign as a distinct, bounded operation, assessed by the continuity of its activity, targets and objectives. Sharing an actor or tools does not by itself merge separate operations. Adding victims, changing tools, adding AI, or receiving a new reporting label does not by itself create a new campaign from an ongoing operation.
+  * Campaign onset is its first malicious action against a target, such as an intrusion or fraudulent solicitation. Planning and tool development alone do not establish onset. Discovery, first reported loss, later encryption, or first use of AI does not reset an earlier onset within the same campaign.
   * Qualifying AI contributions include (non-exhaustive): discovering or developing exploits or pathogen modifications; generating, adapting, or synthesizing malware or biological agents; conducting or scaling social engineering; autonomously selecting targets, propagating, or dispersing; and planning or orchestrating the operation. Routine, long-standing automation (e.g., conventional vulnerability scanners) does not qualify; the AI contribution must be non-trivial to the event's occurrence or scale.
 [PERFECT KNOWLEDGE]
 * Perfect-knowledge clause: Assume we have perfect knowledge of the cause of each event, the intent and identity of the actors involved (including whether an AI system was involved and in what role), and the technical attribution. We want your view on the damages resulting from these events, not on the probability that they would be correctly identified or attributed.  
@@ -3146,7 +3156,11 @@
   * Exclude purely notional losses such as declines in market capitalization or share price that do not correspond to real resource costs. Give all estimates in 2026 USD.  
 * Resolution sources: Assume access to authoritative assessments, which may include estimates from the WHO, World Bank, IMF, national cybersecurity agencies (e.g., CISA, ENISA), major insurers and reinsurers, incident-response and threat-intelligence firms, and academic epidemiological and economic-modeling groups. Where multiple analyses exist, we will use the consensus or median; absent that, we will defer to the majority opinion of a panel of at least five experts.
 [DATES]
-* The incident must have an onset before the end of the defined year.</t>
+* Count only incidents whose onset falls within the specified counting interval, beginning on the elicitation date. All dates refer to UTC calendar dates, inclusive of the stated start and end dates.
+* For six- and twelve-month horizons, the interval ends that many calendar months after the elicitation date. For a fixed-year horizon, it ends on December 31 of the named year. The exact start and end dates are supplied with this forecast. Every later elicitation starts a new counting interval; there is no permanent project-start or calendar-year baseline.
+* Exclude incidents that began before the interval, including their later harms. New reporting, additional losses or later AI involvement does not by itself establish a new incident onset.
+* For each eligible incident, count attributable mortality, equivalent morbidity and economic damages within its first three years after onset, under the severity definitions above. Harm after the interval's end date can count if it falls within that incident's three-year harm window. The horizon is an onset deadline, not a deadline for all harm to occur.
+* These date rules apply to all four incident categories only; the separate large-scale-catastrophe and human-disempowerment questions retain their own date criteria.</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3195,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ladder:cyber:1k</t>
+          <t>ladder:cyber:1k:deaths; ladder:cyber:1k:damages</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3225,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ladder:cyber:10k</t>
+          <t>ladder:cyber:10k:deaths; ladder:cyber:10k:damages</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3256,7 @@
       <c r="F78" s="14" t="n"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ladder:cyber:100k</t>
+          <t>ladder:cyber:100k:deaths; ladder:cyber:100k:damages</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3291,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ladder:cyber:1M</t>
+          <t>ladder:cyber:1M:deaths; ladder:cyber:1M:damages</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3321,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ladder:cyber:10M</t>
+          <t>ladder:cyber:10M:deaths; ladder:cyber:10M:damages</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3351,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ladder:cyber:100M</t>
+          <t>ladder:cyber:100M:deaths; ladder:cyber:100M:damages</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3381,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ladder:cyber:1B</t>
+          <t>ladder:cyber:1B:deaths; ladder:cyber:1B:damages</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3411,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ladder:cyber:100</t>
+          <t>ladder:cyber:100:deaths; ladder:cyber:100:damages</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3441,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ladder:cyber:1k</t>
+          <t>ladder:cyber:1k:deaths; ladder:cyber:1k:damages</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3471,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ladder:cyber:10k</t>
+          <t>ladder:cyber:10k:deaths; ladder:cyber:10k:damages</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3502,7 @@
       <c r="F86" s="14" t="n"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ladder:cyber:100k</t>
+          <t>ladder:cyber:100k:deaths; ladder:cyber:100k:damages</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3537,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ladder:cyber:1M</t>
+          <t>ladder:cyber:1M:deaths; ladder:cyber:1M:damages</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3567,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ladder:cyber:10M</t>
+          <t>ladder:cyber:10M:deaths; ladder:cyber:10M:damages</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3597,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ladder:cyber:100M</t>
+          <t>ladder:cyber:100M:deaths; ladder:cyber:100M:damages</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3627,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ladder:cyber:1B</t>
+          <t>ladder:cyber:1B:deaths; ladder:cyber:1B:damages</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3657,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ladder:cyber:100</t>
+          <t>ladder:cyber:100:deaths; ladder:cyber:100:damages</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3687,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ladder:cyber:1k</t>
+          <t>ladder:cyber:1k:deaths; ladder:cyber:1k:damages</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3717,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ladder:cyber:10k</t>
+          <t>ladder:cyber:10k:deaths; ladder:cyber:10k:damages</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3748,7 @@
       <c r="F94" s="14" t="n"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ladder:cyber:100k</t>
+          <t>ladder:cyber:100k:deaths; ladder:cyber:100k:damages</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3783,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ladder:cyber:1M</t>
+          <t>ladder:cyber:1M:deaths; ladder:cyber:1M:damages</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3813,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ladder:cyber:10M</t>
+          <t>ladder:cyber:10M:deaths; ladder:cyber:10M:damages</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3843,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ladder:cyber:100M</t>
+          <t>ladder:cyber:100M:deaths; ladder:cyber:100M:damages</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3874,7 @@
       <c r="F98" s="14" t="n"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ladder:cyber:1B</t>
+          <t>ladder:cyber:1B:deaths; ladder:cyber:1B:damages</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3904,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ladder:cyber:100</t>
+          <t>ladder:cyber:100:deaths; ladder:cyber:100:damages</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3934,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ladder:cyber:1k</t>
+          <t>ladder:cyber:1k:deaths; ladder:cyber:1k:damages</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3964,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ladder:cyber:10k</t>
+          <t>ladder:cyber:10k:deaths; ladder:cyber:10k:damages</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3995,7 @@
       <c r="F102" s="14" t="n"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ladder:cyber:100k</t>
+          <t>ladder:cyber:100k:deaths; ladder:cyber:100k:damages</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4030,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ladder:cyber:1M</t>
+          <t>ladder:cyber:1M:deaths; ladder:cyber:1M:damages</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4060,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ladder:cyber:10M</t>
+          <t>ladder:cyber:10M:deaths; ladder:cyber:10M:damages</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4090,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ladder:cyber:100M</t>
+          <t>ladder:cyber:100M:deaths; ladder:cyber:100M:damages</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4125,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ladder:cyber:1B</t>
+          <t>ladder:cyber:1B:deaths; ladder:cyber:1B:damages</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4155,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ladder:misalign:100</t>
+          <t>ladder:misalign:100:deaths; ladder:misalign:100:damages</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4169,7 +4183,11 @@
   * Exclude purely notional losses such as declines in market capitalization or share price that do not correspond to real resource costs. Give all estimates in 2026 USD.  
 * Resolution sources: Assume access to authoritative assessments, which may include estimates from the WHO, World Bank, IMF, national cybersecurity agencies (e.g., CISA, ENISA), major insurers and reinsurers, incident-response and threat-intelligence firms, and academic epidemiological and economic-modeling groups. Where multiple analyses exist, we will use the consensus or median; absent that, we will defer to the majority opinion of a panel of at least five experts.
 [DATES]
-* The incident must have an onset before the end of the defined year.</t>
+* Count only incidents whose onset falls within the specified counting interval, beginning on the elicitation date. All dates refer to UTC calendar dates, inclusive of the stated start and end dates.
+* For six- and twelve-month horizons, the interval ends that many calendar months after the elicitation date. For a fixed-year horizon, it ends on December 31 of the named year. The exact start and end dates are supplied with this forecast. Every later elicitation starts a new counting interval; there is no permanent project-start or calendar-year baseline.
+* Exclude incidents that began before the interval, including their later harms. New reporting, additional losses or later AI involvement does not by itself establish a new incident onset.
+* For each eligible incident, count attributable mortality, equivalent morbidity and economic damages within its first three years after onset, under the severity definitions above. Harm after the interval's end date can count if it falls within that incident's three-year harm window. The horizon is an onset deadline, not a deadline for all harm to occur.
+* These date rules apply to all four incident categories only; the separate large-scale-catastrophe and human-disempowerment questions retain their own date criteria.</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4222,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ladder:misalign:1k</t>
+          <t>ladder:misalign:1k:deaths; ladder:misalign:1k:damages</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4252,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ladder:misalign:10k</t>
+          <t>ladder:misalign:10k:deaths; ladder:misalign:10k:damages</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4283,7 @@
       <c r="F110" s="14" t="n"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ladder:misalign:100k</t>
+          <t>ladder:misalign:100k:deaths; ladder:misalign:100k:damages</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4318,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ladder:misalign:1M</t>
+          <t>ladder:misalign:1M:deaths; ladder:misalign:1M:damages</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4348,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ladder:misalign:10M</t>
+          <t>ladder:misalign:10M:deaths; ladder:misalign:10M:damages</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4378,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ladder:misalign:100M</t>
+          <t>ladder:misalign:100M:deaths; ladder:misalign:100M:damages</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4408,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>ladder:misalign:1B</t>
+          <t>ladder:misalign:1B:deaths; ladder:misalign:1B:damages</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4438,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ladder:misalign:100</t>
+          <t>ladder:misalign:100:deaths; ladder:misalign:100:damages</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4468,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ladder:misalign:1k</t>
+          <t>ladder:misalign:1k:deaths; ladder:misalign:1k:damages</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4498,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>ladder:misalign:10k</t>
+          <t>ladder:misalign:10k:deaths; ladder:misalign:10k:damages</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4529,7 @@
       <c r="F118" s="14" t="n"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ladder:misalign:100k</t>
+          <t>ladder:misalign:100k:deaths; ladder:misalign:100k:damages</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4564,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ladder:misalign:1M</t>
+          <t>ladder:misalign:1M:deaths; ladder:misalign:1M:damages</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4594,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ladder:misalign:10M</t>
+          <t>ladder:misalign:10M:deaths; ladder:misalign:10M:damages</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4624,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ladder:misalign:100M</t>
+          <t>ladder:misalign:100M:deaths; ladder:misalign:100M:damages</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4654,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ladder:misalign:1B</t>
+          <t>ladder:misalign:1B:deaths; ladder:misalign:1B:damages</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4684,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ladder:misalign:100</t>
+          <t>ladder:misalign:100:deaths; ladder:misalign:100:damages</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4714,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ladder:misalign:1k</t>
+          <t>ladder:misalign:1k:deaths; ladder:misalign:1k:damages</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4744,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ladder:misalign:10k</t>
+          <t>ladder:misalign:10k:deaths; ladder:misalign:10k:damages</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4775,7 @@
       <c r="F126" s="14" t="n"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ladder:misalign:100k</t>
+          <t>ladder:misalign:100k:deaths; ladder:misalign:100k:damages</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4810,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ladder:misalign:1M</t>
+          <t>ladder:misalign:1M:deaths; ladder:misalign:1M:damages</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4840,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ladder:misalign:10M</t>
+          <t>ladder:misalign:10M:deaths; ladder:misalign:10M:damages</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4870,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>ladder:misalign:100M</t>
+          <t>ladder:misalign:100M:deaths; ladder:misalign:100M:damages</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4900,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ladder:misalign:1B</t>
+          <t>ladder:misalign:1B:deaths; ladder:misalign:1B:damages</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4930,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ladder:misalign:100</t>
+          <t>ladder:misalign:100:deaths; ladder:misalign:100:damages</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4960,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ladder:misalign:1k</t>
+          <t>ladder:misalign:1k:deaths; ladder:misalign:1k:damages</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4990,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>ladder:misalign:10k</t>
+          <t>ladder:misalign:10k:deaths; ladder:misalign:10k:damages</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5021,7 @@
       <c r="F134" s="14" t="n"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ladder:misalign:100k</t>
+          <t>ladder:misalign:100k:deaths; ladder:misalign:100k:damages</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5056,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ladder:misalign:1M</t>
+          <t>ladder:misalign:1M:deaths; ladder:misalign:1M:damages</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5086,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ladder:misalign:10M</t>
+          <t>ladder:misalign:10M:deaths; ladder:misalign:10M:damages</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5116,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>ladder:misalign:100M</t>
+          <t>ladder:misalign:100M:deaths; ladder:misalign:100M:damages</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5151,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ladder:misalign:1B</t>
+          <t>ladder:misalign:1B:deaths; ladder:misalign:1B:damages</t>
         </is>
       </c>
     </row>
